--- a/Intersecciones/excels/LA_LIBERTAD-ASCOPE-ASCOPE.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-ASCOPE-ASCOPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1416,6 +1416,214 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-201231</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>130206</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ASCOPE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAZURI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-7.700389</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-79.4379511</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>130201</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-730348</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>130206</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ASCOPE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAZURI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-7.7461145</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-79.3276811</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>130201</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-730349</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>130206</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ASCOPE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAZURI</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-7.7462772</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-79.3285418</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>130201</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-730350</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>130206</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ASCOPE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAZURI</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-7.7463729</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-79.3290406</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>130201</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
